--- a/stats for com eng/excel files/Ch08-02.xlsx
+++ b/stats for com eng/excel files/Ch08-02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pin/Desktop/joint-repository/stats for com eng/excel files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A3A03F1-9F10-C649-9E29-6862A0E7F24A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C49CC64B-722D-E848-95DE-8C595A535048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="20480" windowHeight="11040" tabRatio="858" activeTab="5" xr2:uid="{1702CB1B-5F51-4566-B5AE-3AF08FAEDD34}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="20480" windowHeight="10960" tabRatio="858" activeTab="2" xr2:uid="{1702CB1B-5F51-4566-B5AE-3AF08FAEDD34}"/>
   </bookViews>
   <sheets>
     <sheet name="Table" sheetId="1" r:id="rId1"/>
@@ -503,17 +503,17 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -6438,8 +6438,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2457451" y="1743074"/>
-          <a:ext cx="2881710" cy="504825"/>
+          <a:off x="2824036" y="1797742"/>
+          <a:ext cx="3194830" cy="520445"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8511,10 +8511,10 @@
       </c>
     </row>
     <row r="23" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="25" t="s">
+      <c r="A23" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="B23" s="26"/>
+      <c r="B23" s="29"/>
       <c r="C23" s="14">
         <f>AVERAGE(C3:C22)</f>
         <v>1.6</v>
@@ -8593,7 +8593,7 @@
       <c r="E2" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="F2" s="27" t="s">
+      <c r="F2" s="25" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8670,7 +8670,7 @@
         <f>AVERAGE(B3:B6)</f>
         <v>98.375</v>
       </c>
-      <c r="F6" s="29"/>
+      <c r="F6" s="27"/>
     </row>
     <row r="7" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
@@ -8691,7 +8691,7 @@
         <f t="shared" ref="E7:E22" si="2">AVERAGE(B4:B7)</f>
         <v>98.375</v>
       </c>
-      <c r="F7" s="29"/>
+      <c r="F7" s="27"/>
     </row>
     <row r="8" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
@@ -8712,7 +8712,7 @@
         <f t="shared" si="2"/>
         <v>99.3</v>
       </c>
-      <c r="F8" s="28">
+      <c r="F8" s="26">
         <f>AVERAGE(B3:B8)</f>
         <v>99</v>
       </c>
@@ -8736,7 +8736,7 @@
         <f t="shared" si="2"/>
         <v>99.474999999999994</v>
       </c>
-      <c r="F9" s="28">
+      <c r="F9" s="26">
         <f t="shared" ref="F9:F22" si="3">AVERAGE(B4:B9)</f>
         <v>98.5</v>
       </c>
@@ -8760,7 +8760,7 @@
         <f t="shared" si="2"/>
         <v>99.3</v>
       </c>
-      <c r="F10" s="28">
+      <c r="F10" s="26">
         <f t="shared" si="3"/>
         <v>98.983333333333334</v>
       </c>
@@ -8784,7 +8784,7 @@
         <f t="shared" si="2"/>
         <v>98.8</v>
       </c>
-      <c r="F11" s="28">
+      <c r="F11" s="26">
         <f t="shared" si="3"/>
         <v>99.266666666666652</v>
       </c>
@@ -8808,7 +8808,7 @@
         <f t="shared" si="2"/>
         <v>98.699999999999989</v>
       </c>
-      <c r="F12" s="28">
+      <c r="F12" s="26">
         <f t="shared" si="3"/>
         <v>99.216666666666654</v>
       </c>
@@ -8832,7 +8832,7 @@
         <f t="shared" si="2"/>
         <v>99.274999999999991</v>
       </c>
-      <c r="F13" s="28">
+      <c r="F13" s="26">
         <f t="shared" si="3"/>
         <v>99.09999999999998</v>
       </c>
@@ -8856,7 +8856,7 @@
         <f t="shared" si="2"/>
         <v>99.524999999999991</v>
       </c>
-      <c r="F14" s="28">
+      <c r="F14" s="26">
         <f t="shared" si="3"/>
         <v>99.133333333333326</v>
       </c>
@@ -8880,7 +8880,7 @@
         <f t="shared" si="2"/>
         <v>99.799999999999983</v>
       </c>
-      <c r="F15" s="28">
+      <c r="F15" s="26">
         <f t="shared" si="3"/>
         <v>99.483333333333334</v>
       </c>
@@ -8904,7 +8904,7 @@
         <f t="shared" si="2"/>
         <v>99.875</v>
       </c>
-      <c r="F16" s="28">
+      <c r="F16" s="26">
         <f t="shared" si="3"/>
         <v>99.59999999999998</v>
       </c>
@@ -8928,7 +8928,7 @@
         <f t="shared" si="2"/>
         <v>98.800000000000011</v>
       </c>
-      <c r="F17" s="28">
+      <c r="F17" s="26">
         <f t="shared" si="3"/>
         <v>99.09999999999998</v>
       </c>
@@ -8952,7 +8952,7 @@
         <f t="shared" si="2"/>
         <v>98.3</v>
       </c>
-      <c r="F18" s="28">
+      <c r="F18" s="26">
         <f t="shared" si="3"/>
         <v>98.866666666666674</v>
       </c>
@@ -8976,7 +8976,7 @@
         <f t="shared" si="2"/>
         <v>98.100000000000009</v>
       </c>
-      <c r="F19" s="28">
+      <c r="F19" s="26">
         <f t="shared" si="3"/>
         <v>98.7</v>
       </c>
@@ -9000,7 +9000,7 @@
         <f t="shared" si="2"/>
         <v>98.85</v>
       </c>
-      <c r="F20" s="28">
+      <c r="F20" s="26">
         <f t="shared" si="3"/>
         <v>99.149999999999991</v>
       </c>
@@ -9024,7 +9024,7 @@
         <f t="shared" si="2"/>
         <v>98.899999999999991</v>
       </c>
-      <c r="F21" s="28">
+      <c r="F21" s="26">
         <f t="shared" si="3"/>
         <v>98.500000000000014</v>
       </c>
@@ -9048,7 +9048,7 @@
         <f t="shared" si="2"/>
         <v>99.974999999999994</v>
       </c>
-      <c r="F22" s="28">
+      <c r="F22" s="26">
         <f t="shared" si="3"/>
         <v>98.933333333333323</v>
       </c>
